--- a/asx_eod_output/Report_XLSX/Report_20260804.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260804.xlsx
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>59.74</v>
+        <v>59.75</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.98</v>
+        <v>-0.97</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>-1.60%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>661023.1</v>
+        <v>661133.75</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10843.7</v>
+        <v>-10733.05</v>
       </c>
     </row>
     <row r="8">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>127.05</v>
+        <v>127.09</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>508200</v>
+        <v>508360</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11000</v>
+        <v>11160</v>
       </c>
     </row>
     <row r="12">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>32.815</v>
+        <v>32.82</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.315</v>
+        <v>0.32</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>42265.72</v>
+        <v>42272.16</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>405.72</v>
+        <v>412.16</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1633137.64</v>
+        <v>1633414.73</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>596.84</v>
+        <v>873.9299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260804.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260804.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.292</v>
+        <v>1.32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.018</v>
+        <v>0.01</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>197909.85</v>
+        <v>202198.92</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-2757.26</v>
+        <v>1531.81</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>150500</v>
+        <v>151200</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2100</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="6">
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.035</v>
+        <v>1.04</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.045</v>
+        <v>0.05</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>5.05%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>57458</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>59469.03</v>
+        <v>59756.32</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2585.61</v>
+        <v>2872.9</v>
       </c>
     </row>
     <row r="7">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>59.75</v>
+        <v>60.52</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.97</v>
+        <v>-0.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.60%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>661133.75</v>
+        <v>669653.8</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10733.05</v>
+        <v>-2213</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>180.48</v>
+        <v>180.72</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -650,24 +650,24 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.75</v>
+        <v>0.765</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7500</v>
+        <v>7650</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>127.09</v>
+        <v>128.83</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2.79</v>
+        <v>4.53</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>3.64%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>508360</v>
+        <v>515320</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11160</v>
+        <v>18120</v>
       </c>
     </row>
     <row r="12">
@@ -704,24 +704,24 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.265</v>
+        <v>0.275</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>5.77%</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>20000</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13">
@@ -758,24 +758,24 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.089</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.23%</t>
+          <t>6.02%</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
         <v>9412</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>837.67</v>
+        <v>828.26</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>56.47</v>
+        <v>47.06</v>
       </c>
     </row>
     <row r="15">
@@ -785,24 +785,24 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-100.00%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
         <v>6000</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-600</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>38.75</v>
+        <v>38.82</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>32.82</v>
+        <v>32.95</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>42272.16</v>
+        <v>42439.6</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>412.16</v>
+        <v>579.6</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1633414.73</v>
+        <v>1655309.17</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>873.9299999999999</v>
+        <v>22768.37</v>
       </c>
     </row>
   </sheetData>
